--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T11:56:44+00:00</t>
+    <t>2025-02-18T15:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:23:31+00:00</t>
+    <t>2025-02-20T16:18:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T16:18:31+00:00</t>
+    <t>2025-02-20T16:32:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T16:32:32+00:00</t>
+    <t>2025-02-20T17:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T17:12:55+00:00</t>
+    <t>2025-02-24T09:51:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="182">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T09:51:08+00:00</t>
+    <t>2025-02-25T09:09:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,10 +311,6 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
-</t>
   </si>
   <si>
     <t>RelatedEntity.typeId.nullFlavor</t>
@@ -1434,7 +1430,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1442,10 +1438,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1543,39 +1539,39 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1626,7 +1622,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1646,39 +1642,39 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1729,7 +1725,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1749,39 +1745,39 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1790,49 +1786,49 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1852,17 +1848,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1880,11 +1876,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1935,7 +1931,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1955,10 +1951,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1985,7 +1981,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2036,7 +2032,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2056,10 +2052,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2085,7 +2081,7 @@
         <v>85</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -2117,7 +2113,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2135,7 +2131,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2155,10 +2151,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2181,10 +2177,10 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -2216,7 +2212,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2234,7 +2230,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2254,10 +2250,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2355,10 +2351,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2387,7 +2383,7 @@
       </c>
       <c r="L15" s="2"/>
       <c r="M15" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2438,7 +2434,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2458,17 +2454,17 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>75</v>
@@ -2486,11 +2482,11 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2541,7 +2537,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2561,17 +2557,17 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>80</v>
@@ -2589,11 +2585,11 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2644,7 +2640,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2664,17 +2660,17 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>80</v>
@@ -2692,11 +2688,11 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2747,7 +2743,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2767,17 +2763,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>75</v>
@@ -2795,11 +2791,11 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2850,7 +2846,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2870,10 +2866,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2896,11 +2892,11 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2951,7 +2947,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -2971,10 +2967,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2997,11 +2993,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3052,7 +3048,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3072,39 +3068,39 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E22" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K22" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="F22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K22" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3155,7 +3151,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3175,39 +3171,39 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E23" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K23" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="F23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H23" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K23" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3258,7 +3254,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3278,17 +3274,17 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>80</v>
@@ -3306,11 +3302,11 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3361,7 +3357,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3381,10 +3377,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3407,10 +3403,10 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
@@ -3462,7 +3458,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3482,10 +3478,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3508,10 +3504,10 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -3563,7 +3559,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3583,10 +3579,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3609,7 +3605,7 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -3662,7 +3658,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3682,10 +3678,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3708,10 +3704,10 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -3763,7 +3759,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T09:09:15+00:00</t>
+    <t>2025-03-05T10:03:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>relatedEntity</t>
+    <t>CDA - relatedEntity</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T10:03:58+00:00</t>
+    <t>2025-04-22T14:43:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -879,42 +879,42 @@
   <dimension ref="A1:AK28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.00390625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="43.00390625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="24.9375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="36.87109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="36.87109375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="21.37890625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="151.96875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="130.28515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="89.85546875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="28.44140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="77.03515625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="24.3828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-22T14:43:59+00:00</t>
+    <t>2025-04-23T09:14:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:14:13+00:00</t>
+    <t>2025-05-19T09:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T09:31:54+00:00</t>
+    <t>2025-05-20T13:20:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -394,7 +394,7 @@
     <t>Rôle joué par la personne.</t>
   </si>
   <si>
-    <t>http://hl7.org/cda/stds/core/ValueSet/CDARoleClassMutualRelationship</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-role-informateur-cisis</t>
   </si>
   <si>
     <t>RelatedEntity.code</t>

--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:20:55+00:00</t>
+    <t>2025-05-23T08:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T08:30:51+00:00</t>
+    <t>2025-05-23T15:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-entity.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
